--- a/data/trans_orig/P6711-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60560</t>
+          <t>59906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>67650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95958</t>
+          <t>95924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47142</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69223</t>
+          <t>68836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26469</t>
+          <t>27530</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47044</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79836</t>
+          <t>81149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110449</t>
+          <t>111785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40150</t>
+          <t>41327</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21003</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51227</t>
+          <t>49884</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93227</t>
+          <t>93425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119357</t>
+          <t>119136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>60353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82964</t>
+          <t>83346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161219</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196940</t>
+          <t>195725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32323</t>
+          <t>32922</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>48667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39829</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59615</t>
+          <t>59728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82873</t>
+          <t>82556</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52532</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99387</t>
+          <t>99288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129527</t>
+          <t>130468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35954</t>
+          <t>35738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>31793</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29716</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53949</t>
+          <t>54187</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>33607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>23360</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52220</t>
+          <t>52870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60948</t>
+          <t>59844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>85130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>31867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51567</t>
+          <t>52498</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97992</t>
+          <t>97252</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130866</t>
+          <t>130832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>46465</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39649</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>55943</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>18758</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38436</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>29536</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53325</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>75622</t>
+          <t>75762</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39822</t>
+          <t>39943</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>82636</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>111314</t>
+          <t>110658</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>31116</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>27198</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>51897</t>
+          <t>50151</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>84218</t>
+          <t>84488</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>36948</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>76633</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>115790</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>46221</t>
+          <t>47491</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>75339</t>
+          <t>74229</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>46203</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>112948</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>91828</t>
+          <t>92448</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>125954</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>81482</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>108904</t>
+          <t>109422</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>182372</t>
+          <t>180574</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>225608</t>
+          <t>224664</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>39932</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38356</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>41253</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>71128</t>
+          <t>71952</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>40144</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>63896</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>94844</t>
+          <t>96907</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>57789</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>103702</t>
+          <t>100373</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>145495</t>
+          <t>142684</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>91630</t>
+          <t>91000</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>125033</t>
+          <t>126056</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>73893</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>106109</t>
+          <t>105920</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>174586</t>
+          <t>173146</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>222741</t>
+          <t>221506</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>116289</t>
+          <t>115967</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>155229</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>67889</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>101347</t>
+          <t>102328</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>194395</t>
+          <t>196972</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>244956</t>
+          <t>245152</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>135140</t>
+          <t>134363</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>187696</t>
+          <t>184469</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>109113</t>
+          <t>111018</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>151900</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>261031</t>
+          <t>258775</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>324660</t>
+          <t>323970</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>104222</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>92366</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>135331</t>
+          <t>135989</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>183177</t>
+          <t>184591</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>237508</t>
+          <t>237444</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>297677</t>
+          <t>297501</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>117339</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>163264</t>
+          <t>163678</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>369878</t>
+          <t>367005</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>444998</t>
+          <t>441440</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>234572</t>
+          <t>232702</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>290776</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>156259</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>208098</t>
+          <t>206109</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>405761</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>481282</t>
+          <t>481335</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>609132</t>
+          <t>607701</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>687135</t>
+          <t>683056</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>388759</t>
+          <t>391257</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>456692</t>
+          <t>457061</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1017359</t>
+          <t>1017357</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1120068</t>
+          <t>1118798</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53652</t>
+          <t>52903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26393</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45874</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65228</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>95568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>23517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29903</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>49463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74093</t>
+          <t>72951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51896</t>
+          <t>52443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86651</t>
+          <t>86434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119076</t>
+          <t>118876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31850</t>
+          <t>32902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35631</t>
+          <t>34535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60121</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>23004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29657</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53982</t>
+          <t>54138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31415</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72636</t>
+          <t>73644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>37705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48832</t>
+          <t>48444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>43272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67949</t>
+          <t>68299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,47 +8254,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>40,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>45359</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>36058</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56956</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>39,9%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>45359</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34395</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>56990</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>39,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83711</t>
+          <t>84635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116712</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63829</t>
+          <t>63862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32002</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48073</t>
+          <t>47918</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73573</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>27804</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36510</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60745</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25095</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>40070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25775</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46494</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49426</t>
+          <t>50127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76343</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>22850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62805</t>
+          <t>64790</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>25479</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73046</t>
+          <t>71518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>99103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52877</t>
+          <t>52914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45778</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68188</t>
+          <t>69227</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>29178</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28263</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>50302</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37091</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>59725</t>
+          <t>59370</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>87024</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>47595</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>42928</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>56724</t>
+          <t>56091</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>88610</t>
+          <t>89479</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>56981</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>86160</t>
+          <t>85159</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>120758</t>
+          <t>121930</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>164682</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>63785</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>95661</t>
+          <t>97181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>49608</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>79174</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>121380</t>
+          <t>120641</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>164851</t>
+          <t>165164</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>65167</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>96661</t>
+          <t>98527</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59428</t>
+          <t>58841</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>90059</t>
+          <t>88874</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>131599</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>175831</t>
+          <t>180984</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>43747</t>
+          <t>44592</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>63182</t>
+          <t>61993</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>97958</t>
+          <t>96993</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>65444</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>98828</t>
+          <t>98740</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>59603</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>107072</t>
+          <t>105753</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>148308</t>
+          <t>150277</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>30535</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>53302</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>51514</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>79768</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>48750</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>77902</t>
+          <t>76066</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>105520</t>
+          <t>107584</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>145128</t>
+          <t>145785</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>131745</t>
+          <t>130991</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>167633</t>
+          <t>166099</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>75219</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>106364</t>
+          <t>104113</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>216447</t>
+          <t>217808</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>262120</t>
+          <t>263067</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>107060</t>
+          <t>105763</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>51258</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>77703</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>132794</t>
+          <t>132600</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>174982</t>
+          <t>175002</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>242179</t>
+          <t>235194</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>169379</t>
+          <t>169877</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>218940</t>
+          <t>222754</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>368278</t>
+          <t>368181</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>440988</t>
+          <t>442030</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>159464</t>
+          <t>156051</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>211966</t>
+          <t>208373</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>123325</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>167301</t>
+          <t>166296</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>297315</t>
+          <t>294506</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>360440</t>
+          <t>363564</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>289795</t>
+          <t>291182</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>355911</t>
+          <t>353689</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>210541</t>
+          <t>209020</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>265192</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>517409</t>
+          <t>517369</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>604552</t>
+          <t>605584</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>287616</t>
+          <t>289026</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>355224</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>183184</t>
+          <t>182198</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>234586</t>
+          <t>234512</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>488044</t>
+          <t>486726</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>570849</t>
+          <t>569846</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>352342</t>
+          <t>352818</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>421121</t>
+          <t>427127</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>227804</t>
+          <t>224737</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>282490</t>
+          <t>284553</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>595372</t>
+          <t>593646</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>689774</t>
+          <t>686868</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6711-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37170</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59906</t>
+          <t>58704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22277</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42136</t>
+          <t>43141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67650</t>
+          <t>66702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>95604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17454</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68836</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48746</t>
+          <t>47166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81149</t>
+          <t>79681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111785</t>
+          <t>109567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>18381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41327</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49884</t>
+          <t>50367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34917</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93425</t>
+          <t>93020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119136</t>
+          <t>120408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83346</t>
+          <t>82600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162791</t>
+          <t>162195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>194512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>32333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>22015</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48667</t>
+          <t>49104</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>32045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54289</t>
+          <t>54617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82556</t>
+          <t>83888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52280</t>
+          <t>52066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99288</t>
+          <t>99123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>130468</t>
+          <t>128881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23134</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35901</t>
+          <t>37049</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54187</t>
+          <t>54696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>34360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23360</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>52580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59844</t>
+          <t>60494</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>85130</t>
+          <t>86074</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>52122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>99369</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130832</t>
+          <t>131529</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26564</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46465</t>
+          <t>45321</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>39381</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34041</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56355</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38665</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17066</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>36199</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52947</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>76947</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39943</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>83572</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>110658</t>
+          <t>111696</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>26051</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>49931</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>35209</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>54248</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>84488</t>
+          <t>84345</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>36948</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>77812</t>
+          <t>75797</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>117437</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>47491</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>73163</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>46810</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>77769</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>111755</t>
+          <t>111605</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>92448</t>
+          <t>90533</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>125954</t>
+          <t>125622</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>81477</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>109422</t>
+          <t>108276</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>180574</t>
+          <t>181527</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>224664</t>
+          <t>225576</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>41253</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>71952</t>
+          <t>71834</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>41251</t>
+          <t>39609</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>63896</t>
+          <t>62495</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>96907</t>
+          <t>95123</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>32186</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>57054</t>
+          <t>57614</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>100373</t>
+          <t>101403</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>142684</t>
+          <t>143452</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>91000</t>
+          <t>91964</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>126056</t>
+          <t>124293</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>73893</t>
+          <t>74618</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>105920</t>
+          <t>106952</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>173146</t>
+          <t>175223</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>221506</t>
+          <t>222362</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>115967</t>
+          <t>115328</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>155229</t>
+          <t>153607</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>69475</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>102328</t>
+          <t>101427</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>196972</t>
+          <t>193944</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>245152</t>
+          <t>244672</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>134363</t>
+          <t>135957</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>184469</t>
+          <t>182864</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>111018</t>
+          <t>109625</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>154316</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>258775</t>
+          <t>260373</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>323970</t>
+          <t>323439</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68244</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>104676</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>57123</t>
+          <t>58140</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>91915</t>
+          <t>92767</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>136483</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>184591</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>237444</t>
+          <t>235039</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>297501</t>
+          <t>296152</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>163678</t>
+          <t>166245</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>367005</t>
+          <t>370370</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>441440</t>
+          <t>447327</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>232702</t>
+          <t>232387</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>290776</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>159369</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>206109</t>
+          <t>209895</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>403035</t>
+          <t>406902</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>481335</t>
+          <t>482757</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>607701</t>
+          <t>605113</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>683056</t>
+          <t>686304</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>391257</t>
+          <t>391861</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>457061</t>
+          <t>454007</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1017357</t>
+          <t>1016766</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1118798</t>
+          <t>1120371</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52903</t>
+          <t>54004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63985</t>
+          <t>63285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95568</t>
+          <t>93339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>22615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>35139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>73624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>31879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86434</t>
+          <t>86126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118876</t>
+          <t>117273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>61342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23004</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54138</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26089</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>46056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73644</t>
+          <t>73984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48444</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>68120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56956</t>
+          <t>56222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84635</t>
+          <t>82985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118222</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>39059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63862</t>
+          <t>63618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47918</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73282</t>
+          <t>75367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60579</t>
+          <t>59236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>35304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>75280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32634</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64790</t>
+          <t>62795</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>73283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99103</t>
+          <t>101619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20527</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>24486</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52914</t>
+          <t>52858</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42613</t>
+          <t>42047</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>30503</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>69227</t>
+          <t>68093</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>27687</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28621</t>
+          <t>28965</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>50302</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>36052</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57295</t>
+          <t>57879</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17938</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33774</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>59370</t>
+          <t>58288</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>85565</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>47595</t>
+          <t>46742</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>56091</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>56850</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>85159</t>
+          <t>87667</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>121930</t>
+          <t>121274</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>164769</t>
+          <t>164449</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>62538</t>
+          <t>62900</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>97181</t>
+          <t>96956</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49608</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>78251</t>
+          <t>78840</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>120641</t>
+          <t>123187</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>165164</t>
+          <t>166421</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>65167</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>98527</t>
+          <t>98863</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>58210</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>88874</t>
+          <t>89531</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>131599</t>
+          <t>131234</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>180984</t>
+          <t>176166</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>64770</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22135</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>61993</t>
+          <t>62623</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>96993</t>
+          <t>96794</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>65444</t>
+          <t>66532</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>98740</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>59603</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>105753</t>
+          <t>105846</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>150277</t>
+          <t>148140</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>27687</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>53302</t>
+          <t>52157</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>51514</t>
+          <t>49438</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>79768</t>
+          <t>79438</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>49320</t>
+          <t>48640</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>76066</t>
+          <t>75726</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>107584</t>
+          <t>106609</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>145785</t>
+          <t>145853</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>130991</t>
+          <t>130153</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>166099</t>
+          <t>166432</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>75122</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>104113</t>
+          <t>105336</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>217808</t>
+          <t>214541</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>263067</t>
+          <t>261666</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>73362</t>
+          <t>74170</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>105763</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>49994</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>77465</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>132600</t>
+          <t>132003</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>175002</t>
+          <t>174420</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>182424</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>235679</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>169877</t>
+          <t>169161</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>222754</t>
+          <t>220399</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>368181</t>
+          <t>368616</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>442030</t>
+          <t>442263</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>156051</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>208373</t>
+          <t>209598</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>123466</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>166296</t>
+          <t>165940</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,47 +12724,47 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>325816</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>293347</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>360650</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>11,93%</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>325816</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>294506</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>363564</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>291182</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>353689</t>
+          <t>359023</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>209020</t>
+          <t>211917</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>265192</t>
+          <t>266281</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>517369</t>
+          <t>517766</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>605584</t>
+          <t>601500</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>289026</t>
+          <t>288436</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>355224</t>
+          <t>354467</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>182198</t>
+          <t>184257</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>234512</t>
+          <t>236757</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>486726</t>
+          <t>487394</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>569846</t>
+          <t>571347</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>352818</t>
+          <t>355631</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>427127</t>
+          <t>425663</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>224737</t>
+          <t>227784</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>284553</t>
+          <t>284347</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>593646</t>
+          <t>598049</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>686868</t>
+          <t>688615</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
